--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -468,16 +468,14 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本1,000.00 万元。</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
         </is>
       </c>
     </row>
@@ -517,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,7 +572,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -583,26 +581,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>9718.861199999999</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>深圳岚锋设立时（2015年7月9日）</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1000</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>9718.861199999999</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>深圳岚锋设立时，出资情况如下：北京岚锋出资1000万元，持股比例100%。</t>
         </is>
       </c>
     </row>
@@ -617,7 +615,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2020年1月18日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -626,7 +624,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -638,6 +636,1222 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>64</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>64</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>64</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>64</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>64</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>64</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>德朴投资</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>64</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>64</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>64</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>64</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>山东龙兴</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>64</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CYZone</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>64</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>苏宁润东</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>64</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>报告期期初（2019年初或2020年初）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>9718.861199999999</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>澜烽一号</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>99</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>99</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>99</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>99</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>99</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>99</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>99</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>99</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>99</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>99</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>本次发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>本次发行前，公司前十名股东持股情况如下：</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2020-01-18</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>全体股东（净资产折股）</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>36000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>1000</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>深圳岚锋全体股东以其拥有的截至 2019年 10月 31日（股改基准日）的净资产 52,728.05万元出资，并按照 1：1.4647 的比例折合股本 36,000.00 万元，其余计入资本公积。</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
         </is>
       </c>
     </row>
@@ -638,22 +638,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -664,31 +664,31 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EARN ACE</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -696,31 +696,31 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QM101</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -728,31 +728,31 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>香港迅雷</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -760,31 +760,31 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>岚沣管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -792,31 +792,31 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>岚烽管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -824,31 +824,31 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>澜烽管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -856,31 +856,31 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>深圳麦高</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -888,31 +888,31 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>汇智同裕</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -920,31 +920,31 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>厦门富凯</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -952,31 +952,31 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>朗玛五号</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -984,31 +984,31 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>朗玛六号</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1016,31 +1016,31 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>朗玛九号</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1048,31 +1048,31 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>朗玛十四号</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1080,31 +1080,31 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>中证投资</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1112,31 +1112,31 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>金石智娱</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1144,31 +1144,31 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>伊敦传媒</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1176,31 +1176,31 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>天正投资</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1208,31 +1208,31 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>利得鑫投</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1240,31 +1240,31 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>德朴投资</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1272,31 +1272,31 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>华金创盈</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1304,31 +1304,31 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>威明投资</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1336,31 +1336,31 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>领誉基石</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1368,31 +1368,31 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>知盛投资</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1400,31 +1400,31 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>山东龙兴</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1432,31 +1432,31 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CYZone</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1464,31 +1464,31 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>苏宁润东</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1496,31 +1496,31 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>报告期期初（2019年初或2020年初）</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
-        <v>9718.861199999999</v>
-      </c>
+          <t>股份公司设立时（2020年1月18日）</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>澜烽一号</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1528,22 +1528,22 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>报告期期初，发行人注册资本为9,718.8612万元，股权结构如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1560,22 +1560,22 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1584,7 +1584,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EARN ACE</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1592,22 +1592,22 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>QM101</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1624,22 +1624,22 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1648,7 +1648,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>香港迅雷</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1656,22 +1656,22 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1680,7 +1680,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>岚沣管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1688,22 +1688,22 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1712,7 +1712,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>岚烽管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1720,22 +1720,22 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1744,7 +1744,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>澜烽管理</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1752,22 +1752,22 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1776,7 +1776,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>深圳麦高</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1784,22 +1784,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1808,7 +1808,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>汇智同裕</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -1816,22 +1816,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>本次发行前（截至招股说明书签署日）</t>
+          <t>股份公司设立时（2020年1月18日）</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1840,7 +1840,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>厦门富凯</t>
+          <t>北京岚锋</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>本次发行前，公司前十名股东持股情况如下：</t>
+          <t>影石创新设立时，股本结构如下：</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,11 +593,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>10777.5453</v>
+      </c>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>深圳岚锋设立时，出资情况如下：北京岚锋出资1000万元，持股比例100%。</t>
@@ -627,9 +631,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -659,9 +669,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -691,9 +707,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I5" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -723,9 +745,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -755,9 +783,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I7" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -787,9 +821,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -819,9 +859,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -851,9 +897,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I10" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -883,9 +935,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I11" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -915,9 +973,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I12" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -947,9 +1011,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I13" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -979,9 +1049,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I14" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1011,9 +1087,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I15" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1043,9 +1125,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I16" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1075,9 +1163,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I17" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1107,9 +1201,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I18" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1139,9 +1239,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I19" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1171,9 +1277,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1203,9 +1315,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1235,9 +1353,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1267,9 +1391,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I23" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1299,9 +1429,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I24" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1331,9 +1467,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1363,9 +1505,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I26" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1395,9 +1543,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I27" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1427,9 +1581,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I28" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1459,9 +1619,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I29" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1491,9 +1657,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1523,9 +1695,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I31" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1555,9 +1733,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I32" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1587,9 +1771,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I33" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1619,9 +1809,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I34" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1651,9 +1847,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I35" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1683,9 +1885,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I36" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1715,9 +1923,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I37" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1747,9 +1961,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I38" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1779,9 +1999,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I39" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1811,9 +2037,15 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I40" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
@@ -1843,12 +2075,918 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2909.5963</v>
+      </c>
+      <c r="I41" t="n">
+        <v>29.9376</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>影石创新设立时，股本结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>99</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>13.3239</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东EARN ACE持有4796.6179万股，持股比例13.3239%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>99</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>9.4001</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东QM101持有3384.0413万股，持股比例9.4001%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>99</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>3143.7542</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>8.732699999999999</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东香港迅雷持有3143.7542万股，持股比例8.7327%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>99</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>4.0667</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东岚沣管理持有1464.0237万股，持股比例4.0667%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>99</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>3.9909</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东华金同达持有1436.7094万股，持股比例3.9909%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>99</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>3.7003</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东厦门富凯持有1332.1116万股，持股比例3.7003%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>99</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>3.2534</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东澜烽管理持有1171.2193万股，持股比例3.2534%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>99</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>2.7125</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东伊敦传媒持有976.4985万股，持股比例2.7125%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>99</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>960.1358</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东领誉基石持有960.1358万股，持股比例2.667%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>99</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>2.5313</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东中证投资持有911.2616万股，持股比例2.5313%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>99</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>2.5312</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东金石智娱持有911.2486万股，持股比例2.5312%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>99</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>1.7737</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东芜湖旷沄持有638.5374万股，持股比例1.7737%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>99</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>1.6682</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛六号持有600.5396万股，持股比例1.6682%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>99</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东天正投资持有584.9989万股，持股比例1.625%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>99</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛五号持有540.4859万股，持股比例1.5013%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>99</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>1.3295</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东汇智同裕持有478.6264万股，持股比例1.3295%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>99</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>1.3001</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东深圳麦高持有468.0393万股，持股比例1.3001%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>99</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>1.2648</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛九号持有455.3182万股，持股比例1.2648%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>99</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛十四号持有224.9975万股，持股比例0.625%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>99</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东利得鑫投持有216.0001万股，持股比例0.6%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>99</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东华金创盈持有157.4973万股，持股比例0.4375%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>99</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东岚烽管理持有145.8319万股，持股比例0.4051%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>99</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东威明投资持有89.9968万股，持股比例0.25%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>99</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>山东龙兴（SS）</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东山东龙兴（SS）持有70.3268万股，持股比例0.1954%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>99</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,11 +469,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -493,11 +492,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -584,7 +581,6 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -625,7 +621,6 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -663,7 +658,6 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -701,7 +695,6 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -739,7 +732,6 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -777,7 +769,6 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -815,7 +806,6 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -853,7 +843,6 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -891,7 +880,6 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -929,7 +917,6 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -967,7 +954,6 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1005,7 +991,6 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1043,7 +1028,6 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1081,7 +1065,6 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1119,7 +1102,6 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1157,7 +1139,6 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1195,7 +1176,6 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1233,7 +1213,6 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1271,7 +1250,6 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1309,7 +1287,6 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1347,7 +1324,6 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1385,7 +1361,6 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1423,7 +1398,6 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1461,7 +1435,6 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1499,7 +1472,6 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1537,7 +1509,6 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1575,7 +1546,6 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1613,7 +1583,6 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1651,7 +1620,6 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1689,7 +1657,6 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1727,7 +1694,6 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1765,7 +1731,6 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1803,7 +1768,6 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1841,7 +1805,6 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,7 +1842,6 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1917,7 +1879,6 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1955,7 +1916,6 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1993,7 +1953,6 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2031,7 +1990,6 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2069,7 +2027,6 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2107,7 +2064,6 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2116,7 +2072,6 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2143,7 +2098,6 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2152,7 +2106,6 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2179,7 +2132,6 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2188,7 +2140,6 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2215,7 +2166,6 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2224,7 +2174,6 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2251,7 +2200,6 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2260,7 +2208,6 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2287,7 +2234,6 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2296,7 +2242,6 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2323,7 +2268,6 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2332,7 +2276,6 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2359,7 +2302,6 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2368,7 +2310,6 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2395,7 +2336,6 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2404,7 +2344,6 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2431,7 +2370,6 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2440,7 +2378,6 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2467,7 +2404,6 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2476,7 +2412,6 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2503,7 +2438,6 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2512,7 +2446,6 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2539,7 +2472,6 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2548,7 +2480,6 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2575,7 +2506,6 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2584,7 +2514,6 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2611,7 +2540,6 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2620,7 +2548,6 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2647,7 +2574,6 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2656,7 +2582,6 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2683,7 +2608,6 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2692,7 +2616,6 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2719,7 +2642,6 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2728,7 +2650,6 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2755,7 +2676,6 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2764,7 +2684,6 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2791,7 +2710,6 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2800,7 +2718,6 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2827,7 +2744,6 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2836,7 +2752,6 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2863,7 +2778,6 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2872,7 +2786,6 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2899,7 +2812,6 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2908,7 +2820,6 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2935,7 +2846,6 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2944,7 +2854,6 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2971,7 +2880,6 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2980,13 +2888,1088 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量2条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量65条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G4" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>409546.7214</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25222.4547</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-395101.812</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="H8" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-10777.5453</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="H10" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="H13" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="H16" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="H17" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="H18" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="H19" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="H20" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="H21" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="H23" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="H24" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="H25" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3143.7542</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3143.7542</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,9 +468,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -492,9 +493,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -581,6 +584,7 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -621,6 +625,7 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -658,6 +663,7 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -695,6 +701,7 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -732,6 +739,7 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -769,6 +777,7 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -806,6 +815,7 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -843,6 +853,7 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -880,6 +891,7 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -917,6 +929,7 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -954,6 +967,7 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -991,6 +1005,7 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1028,6 +1043,7 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1065,6 +1081,7 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1102,6 +1119,7 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1139,6 +1157,7 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1176,6 +1195,7 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1213,6 +1233,7 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1250,6 +1271,7 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1287,6 +1309,7 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1324,6 +1347,7 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1361,6 +1385,7 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1398,6 +1423,7 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1435,6 +1461,7 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1472,6 +1499,7 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1509,6 +1537,7 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1546,6 +1575,7 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1583,6 +1613,7 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1620,6 +1651,7 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1657,6 +1689,7 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1694,6 +1727,7 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1731,6 +1765,7 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1768,6 +1803,7 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1805,6 +1841,7 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1842,6 +1879,7 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,6 +1917,7 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1916,6 +1955,7 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1953,6 +1993,7 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1990,6 +2031,7 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2027,6 +2069,7 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2064,6 +2107,7 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2072,6 +2116,7 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2098,6 +2143,7 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2106,6 +2152,7 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2132,6 +2179,7 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2140,6 +2188,7 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2166,6 +2215,7 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2174,6 +2224,7 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2200,6 +2251,7 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2208,6 +2260,7 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2234,6 +2287,7 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2242,6 +2296,7 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2268,6 +2323,7 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2276,6 +2332,7 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2302,6 +2359,7 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2310,6 +2368,7 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2336,6 +2395,7 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2344,6 +2404,7 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2370,6 +2431,7 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2378,6 +2440,7 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2404,6 +2467,7 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2412,6 +2476,7 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2438,6 +2503,7 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2446,6 +2512,7 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2472,6 +2539,7 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2480,6 +2548,7 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2506,6 +2575,7 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2514,6 +2584,7 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2540,6 +2611,7 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2548,6 +2620,7 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2574,6 +2647,7 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2582,6 +2656,7 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2608,6 +2683,7 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2616,6 +2692,7 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2642,6 +2719,7 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2650,6 +2728,7 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2676,6 +2755,7 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2684,6 +2764,7 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2710,6 +2791,7 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2718,6 +2800,7 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2744,6 +2827,7 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2752,6 +2836,7 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2778,6 +2863,7 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2786,6 +2872,7 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2812,6 +2899,7 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2820,6 +2908,7 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2846,6 +2935,7 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2854,6 +2944,7 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2880,6 +2971,7 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2888,1088 +2980,13 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量2条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量65条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G4" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>409546.7214</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25222.4547</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-395101.812</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EARN ACE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>中证投资</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="H8" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-10777.5453</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>华金创盈</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="H10" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>华金同达</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>厦门富凯</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>天正投资</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="H13" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>威明投资</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>岚沣管理</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>岚烽管理</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="H16" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>朗玛九号</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="H17" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>朗玛五号</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="H18" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>朗玛六号</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="H19" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>汇智同裕</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="H20" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>深圳麦高</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="H21" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>澜烽管理</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1171.2193</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1171.2193</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>知盛投资</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>63.6367</v>
-      </c>
-      <c r="H23" t="n">
-        <v>63.6367</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>芜湖旷沄</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>638.5374</v>
-      </c>
-      <c r="H24" t="n">
-        <v>638.5374</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>金石智娱</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>911.2486</v>
-      </c>
-      <c r="H25" t="n">
-        <v>911.2486</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>香港迅雷</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3143.7542</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3143.7542</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,11 +469,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -493,11 +492,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -584,7 +581,6 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -625,7 +621,6 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -663,7 +658,6 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -701,7 +695,6 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -739,7 +732,6 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -777,7 +769,6 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -815,7 +806,6 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -853,7 +843,6 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -891,7 +880,6 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -929,7 +917,6 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -967,7 +954,6 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1005,7 +991,6 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1043,7 +1028,6 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1081,7 +1065,6 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1119,7 +1102,6 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1157,7 +1139,6 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1195,7 +1176,6 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1233,7 +1213,6 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1271,7 +1250,6 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1309,7 +1287,6 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1347,7 +1324,6 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1385,7 +1361,6 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1423,7 +1398,6 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1461,7 +1435,6 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1499,7 +1472,6 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1537,7 +1509,6 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1575,7 +1546,6 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1613,7 +1583,6 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1651,7 +1620,6 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1689,7 +1657,6 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1727,7 +1694,6 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1765,7 +1731,6 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1803,7 +1768,6 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1841,7 +1805,6 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,7 +1842,6 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1917,7 +1879,6 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1955,7 +1916,6 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1993,7 +1953,6 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2031,7 +1990,6 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2069,7 +2027,6 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2107,7 +2064,6 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2116,7 +2072,6 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2143,7 +2098,6 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2152,7 +2106,6 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2179,7 +2132,6 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2188,7 +2140,6 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2215,7 +2166,6 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2224,7 +2174,6 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2251,7 +2200,6 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2260,7 +2208,6 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2287,7 +2234,6 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2296,7 +2242,6 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2323,7 +2268,6 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2332,7 +2276,6 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2359,7 +2302,6 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2368,7 +2310,6 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2395,7 +2336,6 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2404,7 +2344,6 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2431,7 +2370,6 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2440,7 +2378,6 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2467,7 +2404,6 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2476,7 +2412,6 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2503,7 +2438,6 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2512,7 +2446,6 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2539,7 +2472,6 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2548,7 +2480,6 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2575,7 +2506,6 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2584,7 +2514,6 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2611,7 +2540,6 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2620,7 +2548,6 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2647,7 +2574,6 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2656,7 +2582,6 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2683,7 +2608,6 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2692,7 +2616,6 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2719,7 +2642,6 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2728,7 +2650,6 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2755,7 +2676,6 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2764,7 +2684,6 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2791,7 +2710,6 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2800,7 +2718,6 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2827,7 +2744,6 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2836,7 +2752,6 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2863,7 +2778,6 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2872,7 +2786,6 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2899,7 +2812,6 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2908,7 +2820,6 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2935,7 +2846,6 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2944,7 +2854,6 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2971,7 +2880,6 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2980,13 +2888,1294 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴2条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量65条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G4" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>409546.7214</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25222.4547</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-395101.812</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="H9" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="H10" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-10777.5453</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="H13" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="H16" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>山东龙兴（SS）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="H20" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="H21" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="H22" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="H23" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="H24" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="H25" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="H26" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="H28" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="H29" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="H30" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>960.1358</v>
+      </c>
+      <c r="H31" t="n">
+        <v>960.1358</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,9 +468,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -492,9 +493,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -581,6 +584,7 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -621,6 +625,7 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -658,6 +663,7 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -695,6 +701,7 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -732,6 +739,7 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -769,6 +777,7 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -806,6 +815,7 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -843,6 +853,7 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -880,6 +891,7 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -917,6 +929,7 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -954,6 +967,7 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -991,6 +1005,7 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1028,6 +1043,7 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1065,6 +1081,7 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1102,6 +1119,7 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1139,6 +1157,7 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1176,6 +1195,7 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1213,6 +1233,7 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1250,6 +1271,7 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1287,6 +1309,7 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1324,6 +1347,7 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1361,6 +1385,7 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1398,6 +1423,7 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1435,6 +1461,7 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1472,6 +1499,7 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1509,6 +1537,7 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1546,6 +1575,7 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1583,6 +1613,7 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1620,6 +1651,7 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1657,6 +1689,7 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1694,6 +1727,7 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1731,6 +1765,7 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1768,6 +1803,7 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1805,6 +1841,7 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1842,6 +1879,7 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,6 +1917,7 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1916,6 +1955,7 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1953,6 +1993,7 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1990,6 +2031,7 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2027,6 +2069,7 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2064,6 +2107,7 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2072,6 +2116,7 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2098,6 +2143,7 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2106,6 +2152,7 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2132,6 +2179,7 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2140,6 +2188,7 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2166,6 +2215,7 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2174,6 +2224,7 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2200,6 +2251,7 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2208,6 +2260,7 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2234,6 +2287,7 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2242,6 +2296,7 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2268,6 +2323,7 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2276,6 +2332,7 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2302,6 +2359,7 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2310,6 +2368,7 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2336,6 +2395,7 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2344,6 +2404,7 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2370,6 +2431,7 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2378,6 +2440,7 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2404,6 +2467,7 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2412,6 +2476,7 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2438,6 +2503,7 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2446,6 +2512,7 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2472,6 +2539,7 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2480,6 +2548,7 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2506,6 +2575,7 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2514,6 +2584,7 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2540,6 +2611,7 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2548,6 +2620,7 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2574,6 +2647,7 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2582,6 +2656,7 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2608,6 +2683,7 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2616,6 +2692,7 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2642,6 +2719,7 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2650,6 +2728,7 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2676,6 +2755,7 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2684,6 +2764,7 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2710,6 +2791,7 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2718,6 +2800,7 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2744,6 +2827,7 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2752,6 +2836,7 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2778,6 +2863,7 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2786,6 +2872,7 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2812,6 +2899,7 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2820,6 +2908,7 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2846,6 +2935,7 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2854,6 +2944,7 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2880,6 +2971,7 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2888,1294 +2980,13 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴2条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量65条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G4" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>409546.7214</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="G6" t="n">
-        <v>25222.4547</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-395101.812</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EARN ACE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>QM101</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3384.0413</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3384.0413</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>中证投资</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="H9" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>伊敦传媒</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>976.4985</v>
-      </c>
-      <c r="H10" t="n">
-        <v>976.4985</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>利得鑫投</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>216.0001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>216.0001</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-10777.5453</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>华金创盈</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="H13" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>华金同达</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>厦门富凯</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>天正投资</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="H16" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>威明投资</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>山东龙兴（SS）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>70.32680000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>70.32680000000001</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>岚沣管理</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>岚烽管理</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="H20" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>朗玛九号</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="H21" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>朗玛五号</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="H22" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>朗玛六号</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="H23" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>朗玛十四号</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>224.9975</v>
-      </c>
-      <c r="H24" t="n">
-        <v>224.9975</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>汇智同裕</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="H25" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>深圳麦高</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="H26" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>澜烽管理</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1171.2193</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1171.2193</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>知盛投资</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>63.6367</v>
-      </c>
-      <c r="H28" t="n">
-        <v>63.6367</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>芜湖旷沄</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>638.5374</v>
-      </c>
-      <c r="H29" t="n">
-        <v>638.5374</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>金石智娱</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>911.2486</v>
-      </c>
-      <c r="H30" t="n">
-        <v>911.2486</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>领誉基石</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>960.1358</v>
-      </c>
-      <c r="H31" t="n">
-        <v>960.1358</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,11 +469,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -493,11 +492,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -584,7 +581,6 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -625,7 +621,6 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -663,7 +658,6 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -701,7 +695,6 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -739,7 +732,6 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -777,7 +769,6 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -815,7 +806,6 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -853,7 +843,6 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -891,7 +880,6 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -929,7 +917,6 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -967,7 +954,6 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1005,7 +991,6 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1043,7 +1028,6 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1081,7 +1065,6 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1119,7 +1102,6 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1157,7 +1139,6 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1195,7 +1176,6 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1233,7 +1213,6 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1271,7 +1250,6 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1309,7 +1287,6 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1347,7 +1324,6 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1385,7 +1361,6 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1423,7 +1398,6 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1461,7 +1435,6 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1499,7 +1472,6 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1537,7 +1509,6 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1575,7 +1546,6 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1613,7 +1583,6 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1651,7 +1620,6 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1689,7 +1657,6 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1727,7 +1694,6 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1765,7 +1731,6 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1803,7 +1768,6 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1841,7 +1805,6 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,7 +1842,6 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1917,7 +1879,6 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1955,7 +1916,6 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1993,7 +1953,6 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2031,7 +1990,6 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2069,7 +2027,6 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2107,7 +2064,6 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2116,7 +2072,6 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2143,7 +2098,6 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2152,7 +2106,6 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2179,7 +2132,6 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2188,7 +2140,6 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2215,7 +2166,6 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2224,7 +2174,6 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2251,7 +2200,6 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2260,7 +2208,6 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2287,7 +2234,6 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2296,7 +2242,6 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2323,7 +2268,6 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2332,7 +2276,6 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2359,7 +2302,6 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2368,7 +2310,6 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2395,7 +2336,6 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2404,7 +2344,6 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2431,7 +2370,6 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2440,7 +2378,6 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2467,7 +2404,6 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2476,7 +2412,6 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2503,7 +2438,6 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2512,7 +2446,6 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2539,7 +2472,6 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2548,7 +2480,6 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2575,7 +2506,6 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2584,7 +2514,6 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2611,7 +2540,6 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2620,7 +2548,6 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2647,7 +2574,6 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2656,7 +2582,6 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2683,7 +2608,6 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2692,7 +2616,6 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2719,7 +2642,6 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2728,7 +2650,6 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2755,7 +2676,6 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2764,7 +2684,6 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2791,7 +2710,6 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2800,7 +2718,6 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2827,7 +2744,6 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2836,7 +2752,6 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2863,7 +2778,6 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2872,7 +2786,6 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2899,7 +2812,6 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2908,7 +2820,6 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2935,7 +2846,6 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2944,7 +2854,6 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2971,7 +2880,6 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2980,7 +2888,6 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
@@ -2989,6 +2896,306 @@
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴2条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量65条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="I4" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>409546.7214</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25222.4547</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-395101.812</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1股东</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>比例合计29.94%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>10777.55</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>39股东</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>比例合计1167.57%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>420324.27</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25股东</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>比例合计70.06%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>25222.45</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,9 +468,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -492,9 +493,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -581,6 +584,7 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -621,6 +625,7 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -658,6 +663,7 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -695,6 +701,7 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -732,6 +739,7 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -769,6 +777,7 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -806,6 +815,7 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -843,6 +853,7 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -880,6 +891,7 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -917,6 +929,7 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -954,6 +967,7 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -991,6 +1005,7 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1028,6 +1043,7 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1065,6 +1081,7 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1102,6 +1119,7 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1139,6 +1157,7 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1176,6 +1195,7 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1213,6 +1233,7 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1250,6 +1271,7 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1287,6 +1309,7 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1324,6 +1347,7 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1361,6 +1385,7 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1398,6 +1423,7 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1435,6 +1461,7 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1472,6 +1499,7 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1509,6 +1537,7 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1546,6 +1575,7 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1583,6 +1613,7 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1620,6 +1651,7 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1657,6 +1689,7 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1694,6 +1727,7 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1731,6 +1765,7 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1768,6 +1803,7 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1805,6 +1841,7 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1842,6 +1879,7 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,6 +1917,7 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1916,6 +1955,7 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1953,6 +1993,7 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1990,6 +2031,7 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2027,6 +2069,7 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2064,6 +2107,7 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2072,6 +2116,7 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2098,6 +2143,7 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2106,6 +2152,7 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2132,6 +2179,7 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2140,6 +2188,7 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2166,6 +2215,7 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2174,6 +2224,7 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2200,6 +2251,7 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2208,6 +2260,7 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2234,6 +2287,7 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2242,6 +2296,7 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2268,6 +2323,7 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2276,6 +2332,7 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2302,6 +2359,7 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2310,6 +2368,7 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2336,6 +2395,7 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2344,6 +2404,7 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2370,6 +2431,7 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2378,6 +2440,7 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2404,6 +2467,7 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2412,6 +2476,7 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2438,6 +2503,7 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2446,6 +2512,7 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2472,6 +2539,7 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2480,6 +2548,7 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2506,6 +2575,7 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2514,6 +2584,7 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2540,6 +2611,7 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2548,6 +2620,7 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2574,6 +2647,7 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2582,6 +2656,7 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2608,6 +2683,7 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2616,6 +2692,7 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2642,6 +2719,7 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2650,6 +2728,7 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2676,6 +2755,7 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2684,6 +2764,7 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2710,6 +2791,7 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2718,6 +2800,7 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2744,6 +2827,7 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2752,6 +2836,7 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2778,6 +2863,7 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2786,6 +2872,7 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2812,6 +2899,7 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2820,6 +2908,7 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2846,6 +2935,7 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2854,6 +2944,7 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2880,6 +2971,7 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2888,6 +2980,7 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
@@ -2896,306 +2989,6 @@
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴2条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量65条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="I4" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="J4" t="n">
-        <v>409546.7214</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25222.4547</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-395101.812</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1股东</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>比例合计29.94%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>10777.55</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>39股东</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>比例合计1167.57%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>420324.27</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>25股东</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>比例合计70.06%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>25222.45</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,11 +469,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -493,11 +492,9 @@
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -584,7 +581,6 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -625,7 +621,6 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -663,7 +658,6 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -701,7 +695,6 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -739,7 +732,6 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -777,7 +769,6 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -815,7 +806,6 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -853,7 +843,6 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -891,7 +880,6 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -929,7 +917,6 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -967,7 +954,6 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1005,7 +991,6 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1043,7 +1028,6 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1081,7 +1065,6 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1119,7 +1102,6 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1157,7 +1139,6 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1195,7 +1176,6 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1233,7 +1213,6 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1271,7 +1250,6 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1309,7 +1287,6 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1347,7 +1324,6 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1385,7 +1361,6 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1423,7 +1398,6 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1461,7 +1435,6 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1499,7 +1472,6 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1537,7 +1509,6 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1575,7 +1546,6 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1613,7 +1583,6 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1651,7 +1620,6 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1689,7 +1657,6 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1727,7 +1694,6 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1765,7 +1731,6 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1803,7 +1768,6 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1841,7 +1805,6 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,7 +1842,6 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1917,7 +1879,6 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1955,7 +1916,6 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1993,7 +1953,6 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2031,7 +1990,6 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2069,7 +2027,6 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2107,7 +2064,6 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2116,7 +2072,6 @@
       <c r="G42" t="n">
         <v>4796.6179</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>13.3239</v>
       </c>
@@ -2143,7 +2098,6 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2152,7 +2106,6 @@
       <c r="G43" t="n">
         <v>3384.0413</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9.4001</v>
       </c>
@@ -2179,7 +2132,6 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2188,7 +2140,6 @@
       <c r="G44" t="n">
         <v>3143.7542</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
       </c>
@@ -2215,7 +2166,6 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2224,7 +2174,6 @@
       <c r="G45" t="n">
         <v>1464.0237</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>4.0667</v>
       </c>
@@ -2251,7 +2200,6 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2260,7 +2208,6 @@
       <c r="G46" t="n">
         <v>1436.7094</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>3.9909</v>
       </c>
@@ -2287,7 +2234,6 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2296,7 +2242,6 @@
       <c r="G47" t="n">
         <v>1332.1116</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>3.7003</v>
       </c>
@@ -2323,7 +2268,6 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2332,7 +2276,6 @@
       <c r="G48" t="n">
         <v>1171.2193</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>3.2534</v>
       </c>
@@ -2359,7 +2302,6 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2368,7 +2310,6 @@
       <c r="G49" t="n">
         <v>976.4985</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>2.7125</v>
       </c>
@@ -2395,7 +2336,6 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2404,7 +2344,6 @@
       <c r="G50" t="n">
         <v>960.1358</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>2.667</v>
       </c>
@@ -2431,7 +2370,6 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2440,7 +2378,6 @@
       <c r="G51" t="n">
         <v>911.2616</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>2.5313</v>
       </c>
@@ -2467,7 +2404,6 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2476,7 +2412,6 @@
       <c r="G52" t="n">
         <v>911.2486</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>2.5312</v>
       </c>
@@ -2503,7 +2438,6 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2512,7 +2446,6 @@
       <c r="G53" t="n">
         <v>638.5374</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1.7737</v>
       </c>
@@ -2539,7 +2472,6 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2548,7 +2480,6 @@
       <c r="G54" t="n">
         <v>600.5396</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1.6682</v>
       </c>
@@ -2575,7 +2506,6 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2584,7 +2514,6 @@
       <c r="G55" t="n">
         <v>584.9989</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1.625</v>
       </c>
@@ -2611,7 +2540,6 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2620,7 +2548,6 @@
       <c r="G56" t="n">
         <v>540.4859</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1.5013</v>
       </c>
@@ -2647,7 +2574,6 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2656,7 +2582,6 @@
       <c r="G57" t="n">
         <v>478.6264</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1.3295</v>
       </c>
@@ -2683,7 +2608,6 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2692,7 +2616,6 @@
       <c r="G58" t="n">
         <v>468.0393</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>1.3001</v>
       </c>
@@ -2719,7 +2642,6 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2728,7 +2650,6 @@
       <c r="G59" t="n">
         <v>455.3182</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1.2648</v>
       </c>
@@ -2755,7 +2676,6 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2764,7 +2684,6 @@
       <c r="G60" t="n">
         <v>224.9975</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0.625</v>
       </c>
@@ -2791,7 +2710,6 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2800,7 +2718,6 @@
       <c r="G61" t="n">
         <v>216.0001</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.6</v>
       </c>
@@ -2827,7 +2744,6 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2836,7 +2752,6 @@
       <c r="G62" t="n">
         <v>157.4973</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0.4375</v>
       </c>
@@ -2863,7 +2778,6 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2872,7 +2786,6 @@
       <c r="G63" t="n">
         <v>145.8319</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0.4051</v>
       </c>
@@ -2899,7 +2812,6 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2908,7 +2820,6 @@
       <c r="G64" t="n">
         <v>89.99679999999999</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0.25</v>
       </c>
@@ -2935,7 +2846,6 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2944,7 +2854,6 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2971,7 +2880,6 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2980,13 +2888,203 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴2条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量65条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让1条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1股东</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>比例合计29.94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>39股东</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>比例合计1167.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25股东</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>比例合计70.06%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -2908,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2919,20 +2919,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2947,17 +2972,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴2条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2条,字段完整</t>
         </is>
       </c>
     </row>
@@ -2970,121 +3000,980 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量65条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>65条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让1条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G4" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>409546.7214</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1股东</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>420324.2667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25222.4547</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-395101.812</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>比例合计29.94%</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39股东</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>比例合计1167.57%</t>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="H9" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="H10" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10777.5453</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-10777.5453</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="H13" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="H16" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>山东龙兴（SS）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="H20" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="H21" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="H22" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="H23" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="H24" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="H25" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="H26" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t1-&gt;发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>ratio_check</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>发行前（第99页）</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1股东</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t0比例合计29.94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>39股东</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t1比例合计1167.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>25股东</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>比例合计70.06%</t>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>发行前（第99页）比例合计70.06%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,9 +468,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -492,9 +493,11 @@
           <t>北京岚锋</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1000</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
@@ -581,6 +584,7 @@
           <t>深圳岚锋设立时（2015年7月9日）</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
@@ -621,6 +625,7 @@
       <c r="D3" t="n">
         <v>36000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -658,6 +663,7 @@
       <c r="D4" t="n">
         <v>36000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -695,6 +701,7 @@
       <c r="D5" t="n">
         <v>36000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -732,6 +739,7 @@
       <c r="D6" t="n">
         <v>36000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -769,6 +777,7 @@
       <c r="D7" t="n">
         <v>36000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -806,6 +815,7 @@
       <c r="D8" t="n">
         <v>36000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -843,6 +853,7 @@
       <c r="D9" t="n">
         <v>36000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -880,6 +891,7 @@
       <c r="D10" t="n">
         <v>36000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -917,6 +929,7 @@
       <c r="D11" t="n">
         <v>36000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -954,6 +967,7 @@
       <c r="D12" t="n">
         <v>36000</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -991,6 +1005,7 @@
       <c r="D13" t="n">
         <v>36000</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1028,6 +1043,7 @@
       <c r="D14" t="n">
         <v>36000</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1065,6 +1081,7 @@
       <c r="D15" t="n">
         <v>36000</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1102,6 +1119,7 @@
       <c r="D16" t="n">
         <v>36000</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1139,6 +1157,7 @@
       <c r="D17" t="n">
         <v>36000</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1176,6 +1195,7 @@
       <c r="D18" t="n">
         <v>36000</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1213,6 +1233,7 @@
       <c r="D19" t="n">
         <v>36000</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1250,6 +1271,7 @@
       <c r="D20" t="n">
         <v>36000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1287,6 +1309,7 @@
       <c r="D21" t="n">
         <v>36000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1324,6 +1347,7 @@
       <c r="D22" t="n">
         <v>36000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1361,6 +1385,7 @@
       <c r="D23" t="n">
         <v>36000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1398,6 +1423,7 @@
       <c r="D24" t="n">
         <v>36000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1435,6 +1461,7 @@
       <c r="D25" t="n">
         <v>36000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1472,6 +1499,7 @@
       <c r="D26" t="n">
         <v>36000</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1509,6 +1537,7 @@
       <c r="D27" t="n">
         <v>36000</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1546,6 +1575,7 @@
       <c r="D28" t="n">
         <v>36000</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1583,6 +1613,7 @@
       <c r="D29" t="n">
         <v>36000</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1620,6 +1651,7 @@
       <c r="D30" t="n">
         <v>36000</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1657,6 +1689,7 @@
       <c r="D31" t="n">
         <v>36000</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1694,6 +1727,7 @@
       <c r="D32" t="n">
         <v>36000</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1731,6 +1765,7 @@
       <c r="D33" t="n">
         <v>36000</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1768,6 +1803,7 @@
       <c r="D34" t="n">
         <v>36000</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1805,6 +1841,7 @@
       <c r="D35" t="n">
         <v>36000</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1842,6 +1879,7 @@
       <c r="D36" t="n">
         <v>36000</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1879,6 +1917,7 @@
       <c r="D37" t="n">
         <v>36000</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1916,6 +1955,7 @@
       <c r="D38" t="n">
         <v>36000</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1953,6 +1993,7 @@
       <c r="D39" t="n">
         <v>36000</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -1990,6 +2031,7 @@
       <c r="D40" t="n">
         <v>36000</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2027,6 +2069,7 @@
       <c r="D41" t="n">
         <v>36000</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>北京岚锋</t>
@@ -2064,6 +2107,7 @@
       <c r="D42" t="n">
         <v>36000</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>EARN ACE</t>
@@ -2071,6 +2115,9 @@
       </c>
       <c r="G42" t="n">
         <v>4796.6179</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1294.9351</v>
       </c>
       <c r="I42" t="n">
         <v>13.3239</v>
@@ -2098,6 +2145,7 @@
       <c r="D43" t="n">
         <v>36000</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>QM101</t>
@@ -2105,6 +2153,9 @@
       </c>
       <c r="G43" t="n">
         <v>3384.0413</v>
+      </c>
+      <c r="H43" t="n">
+        <v>913.5841</v>
       </c>
       <c r="I43" t="n">
         <v>9.4001</v>
@@ -2132,6 +2183,7 @@
       <c r="D44" t="n">
         <v>36000</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>香港迅雷</t>
@@ -2139,6 +2191,9 @@
       </c>
       <c r="G44" t="n">
         <v>3143.7542</v>
+      </c>
+      <c r="H44" t="n">
+        <v>848.7142</v>
       </c>
       <c r="I44" t="n">
         <v>8.732699999999999</v>
@@ -2166,6 +2221,7 @@
       <c r="D45" t="n">
         <v>36000</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>岚沣管理</t>
@@ -2173,6 +2229,9 @@
       </c>
       <c r="G45" t="n">
         <v>1464.0237</v>
+      </c>
+      <c r="H45" t="n">
+        <v>395.2401</v>
       </c>
       <c r="I45" t="n">
         <v>4.0667</v>
@@ -2200,6 +2259,7 @@
       <c r="D46" t="n">
         <v>36000</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>华金同达</t>
@@ -2207,6 +2267,9 @@
       </c>
       <c r="G46" t="n">
         <v>1436.7094</v>
+      </c>
+      <c r="H46" t="n">
+        <v>387.8661</v>
       </c>
       <c r="I46" t="n">
         <v>3.9909</v>
@@ -2234,6 +2297,7 @@
       <c r="D47" t="n">
         <v>36000</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>厦门富凯</t>
@@ -2241,6 +2305,9 @@
       </c>
       <c r="G47" t="n">
         <v>1332.1116</v>
+      </c>
+      <c r="H47" t="n">
+        <v>359.628</v>
       </c>
       <c r="I47" t="n">
         <v>3.7003</v>
@@ -2268,6 +2335,7 @@
       <c r="D48" t="n">
         <v>36000</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>澜烽管理</t>
@@ -2275,6 +2343,9 @@
       </c>
       <c r="G48" t="n">
         <v>1171.2193</v>
+      </c>
+      <c r="H48" t="n">
+        <v>316.1921</v>
       </c>
       <c r="I48" t="n">
         <v>3.2534</v>
@@ -2302,6 +2373,7 @@
       <c r="D49" t="n">
         <v>36000</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>伊敦传媒</t>
@@ -2309,6 +2381,9 @@
       </c>
       <c r="G49" t="n">
         <v>976.4985</v>
+      </c>
+      <c r="H49" t="n">
+        <v>263.6237</v>
       </c>
       <c r="I49" t="n">
         <v>2.7125</v>
@@ -2336,6 +2411,7 @@
       <c r="D50" t="n">
         <v>36000</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>领誉基石</t>
@@ -2343,6 +2419,9 @@
       </c>
       <c r="G50" t="n">
         <v>960.1358</v>
+      </c>
+      <c r="H50" t="n">
+        <v>259.2063</v>
       </c>
       <c r="I50" t="n">
         <v>2.667</v>
@@ -2370,6 +2449,7 @@
       <c r="D51" t="n">
         <v>36000</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>中证投资</t>
@@ -2377,6 +2457,9 @@
       </c>
       <c r="G51" t="n">
         <v>911.2616</v>
+      </c>
+      <c r="H51" t="n">
+        <v>246.0118</v>
       </c>
       <c r="I51" t="n">
         <v>2.5313</v>
@@ -2404,6 +2487,7 @@
       <c r="D52" t="n">
         <v>36000</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>金石智娱</t>
@@ -2411,6 +2495,9 @@
       </c>
       <c r="G52" t="n">
         <v>911.2486</v>
+      </c>
+      <c r="H52" t="n">
+        <v>246.0083</v>
       </c>
       <c r="I52" t="n">
         <v>2.5312</v>
@@ -2438,6 +2525,7 @@
       <c r="D53" t="n">
         <v>36000</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>芜湖旷沄</t>
@@ -2445,6 +2533,9 @@
       </c>
       <c r="G53" t="n">
         <v>638.5374</v>
+      </c>
+      <c r="H53" t="n">
+        <v>172.3849</v>
       </c>
       <c r="I53" t="n">
         <v>1.7737</v>
@@ -2472,6 +2563,7 @@
       <c r="D54" t="n">
         <v>36000</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>朗玛六号</t>
@@ -2479,6 +2571,9 @@
       </c>
       <c r="G54" t="n">
         <v>600.5396</v>
+      </c>
+      <c r="H54" t="n">
+        <v>162.1267</v>
       </c>
       <c r="I54" t="n">
         <v>1.6682</v>
@@ -2506,6 +2601,7 @@
       <c r="D55" t="n">
         <v>36000</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>天正投资</t>
@@ -2513,6 +2609,9 @@
       </c>
       <c r="G55" t="n">
         <v>584.9989</v>
+      </c>
+      <c r="H55" t="n">
+        <v>157.9312</v>
       </c>
       <c r="I55" t="n">
         <v>1.625</v>
@@ -2540,6 +2639,7 @@
       <c r="D56" t="n">
         <v>36000</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>朗玛五号</t>
@@ -2547,6 +2647,9 @@
       </c>
       <c r="G56" t="n">
         <v>540.4859</v>
+      </c>
+      <c r="H56" t="n">
+        <v>145.9141</v>
       </c>
       <c r="I56" t="n">
         <v>1.5013</v>
@@ -2574,6 +2677,7 @@
       <c r="D57" t="n">
         <v>36000</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>汇智同裕</t>
@@ -2581,6 +2685,9 @@
       </c>
       <c r="G57" t="n">
         <v>478.6264</v>
+      </c>
+      <c r="H57" t="n">
+        <v>51.7155</v>
       </c>
       <c r="I57" t="n">
         <v>1.3295</v>
@@ -2608,6 +2715,7 @@
       <c r="D58" t="n">
         <v>36000</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>深圳麦高</t>
@@ -2615,6 +2723,9 @@
       </c>
       <c r="G58" t="n">
         <v>468.0393</v>
+      </c>
+      <c r="H58" t="n">
+        <v>126.3558</v>
       </c>
       <c r="I58" t="n">
         <v>1.3001</v>
@@ -2642,6 +2753,7 @@
       <c r="D59" t="n">
         <v>36000</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>朗玛九号</t>
@@ -2649,6 +2761,9 @@
       </c>
       <c r="G59" t="n">
         <v>455.3182</v>
+      </c>
+      <c r="H59" t="n">
+        <v>122.9215</v>
       </c>
       <c r="I59" t="n">
         <v>1.2648</v>
@@ -2676,6 +2791,7 @@
       <c r="D60" t="n">
         <v>36000</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>朗玛十四号</t>
@@ -2683,6 +2799,9 @@
       </c>
       <c r="G60" t="n">
         <v>224.9975</v>
+      </c>
+      <c r="H60" t="n">
+        <v>60.7422</v>
       </c>
       <c r="I60" t="n">
         <v>0.625</v>
@@ -2710,6 +2829,7 @@
       <c r="D61" t="n">
         <v>36000</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>利得鑫投</t>
@@ -2717,6 +2837,9 @@
       </c>
       <c r="G61" t="n">
         <v>216.0001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>58.3132</v>
       </c>
       <c r="I61" t="n">
         <v>0.6</v>
@@ -2744,6 +2867,7 @@
       <c r="D62" t="n">
         <v>36000</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>华金创盈</t>
@@ -2751,6 +2875,9 @@
       </c>
       <c r="G62" t="n">
         <v>157.4973</v>
+      </c>
+      <c r="H62" t="n">
+        <v>42.5193</v>
       </c>
       <c r="I62" t="n">
         <v>0.4375</v>
@@ -2778,6 +2905,7 @@
       <c r="D63" t="n">
         <v>36000</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>岚烽管理</t>
@@ -2785,6 +2913,9 @@
       </c>
       <c r="G63" t="n">
         <v>145.8319</v>
+      </c>
+      <c r="H63" t="n">
+        <v>39.37</v>
       </c>
       <c r="I63" t="n">
         <v>0.4051</v>
@@ -2812,6 +2943,7 @@
       <c r="D64" t="n">
         <v>36000</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>威明投资</t>
@@ -2819,6 +2951,9 @@
       </c>
       <c r="G64" t="n">
         <v>89.99679999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24.2963</v>
       </c>
       <c r="I64" t="n">
         <v>0.25</v>
@@ -2846,6 +2981,7 @@
       <c r="D65" t="n">
         <v>36000</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>山东龙兴（SS）</t>
@@ -2854,6 +2990,7 @@
       <c r="G65" t="n">
         <v>70.32680000000001</v>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0.1954</v>
       </c>
@@ -2880,6 +3017,7 @@
       <c r="D66" t="n">
         <v>36000</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>知盛投资</t>
@@ -2888,1092 +3026,15 @@
       <c r="G66" t="n">
         <v>63.6367</v>
       </c>
+      <c r="H66" t="n">
+        <v>17.1799</v>
+      </c>
       <c r="I66" t="n">
         <v>0.1768</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东/认购方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额(万股)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2条,字段完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>65条,t0存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G4" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>409546.7214</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>420324.2667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25222.4547</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-395101.812</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EARN ACE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4796.6179</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>QM101</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3384.0413</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3384.0413</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>中证投资</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="H9" t="n">
-        <v>911.2616</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>伊敦传媒</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>976.4985</v>
-      </c>
-      <c r="H10" t="n">
-        <v>976.4985</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>利得鑫投</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>216.0001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>216.0001</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-10777.5453</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>华金创盈</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="H13" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>华金同达</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1436.7094</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>厦门富凯</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1332.1116</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>天正投资</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="H16" t="n">
-        <v>584.9989</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>威明投资</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>山东龙兴（SS）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>70.32680000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>70.32680000000001</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>岚沣管理</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1464.0237</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>岚烽管理</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="H20" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>朗玛九号</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="H21" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>朗玛五号</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="H22" t="n">
-        <v>540.4859</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>朗玛六号</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="H23" t="n">
-        <v>600.5396</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>朗玛十四号</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>224.9975</v>
-      </c>
-      <c r="H24" t="n">
-        <v>224.9975</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>汇智同裕</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="H25" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>深圳麦高</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="H26" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>t1-&gt;发行前（第99页）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1股东</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>t0比例合计29.94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>39股东</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>t1比例合计1167.57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>25股东</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>发行前（第99页）比例合计70.06%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -475,7 +475,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。 [公司设立/股改, 非增资事件, 认购数量和价格不适用]</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。 [公司设立/股改, 非增资事件, 认购数量和价格不适用]</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -475,7 +475,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。 [公司设立/股改, 非增资事件, 认购数量和价格不适用]</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。 [公司设立/股改, 非增资事件, 认购数量和价格不适用]</t>
+          <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,1056 +572,890 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>深圳岚锋设立时（2015年7月9日）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>29.9376</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>深圳岚锋设立时，出资情况如下：北京岚锋出资1000万元，持股比例100%。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>29.9376</v>
+        <v>13.3239</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>29.9376</v>
+        <v>9.4001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>29.9376</v>
+        <v>8.732699999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>29.9376</v>
+        <v>4.0667</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>29.9376</v>
+        <v>3.9909</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>29.9376</v>
+        <v>3.7003</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>29.9376</v>
+        <v>3.2534</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>29.9376</v>
+        <v>2.7125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>29.9376</v>
+        <v>2.667</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>29.9376</v>
+        <v>2.5313</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>29.9376</v>
+        <v>2.5312</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>29.9376</v>
+        <v>1.7737</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>29.9376</v>
+        <v>1.6682</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>29.9376</v>
+        <v>1.625</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>29.9376</v>
+        <v>1.5013</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>29.9376</v>
+        <v>1.3001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>29.9376</v>
+        <v>1.2648</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>德朴投资</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>29.9376</v>
+        <v>0.7974</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>29.9376</v>
+        <v>0.625</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>29.9376</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>29.9376</v>
+        <v>0.5321</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>29.9376</v>
+        <v>0.4375</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>29.9376</v>
+        <v>0.4051</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>29.9376</v>
+        <v>0.25</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>山东龙兴(SS)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>29.9376</v>
+        <v>0.1954</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>10777.5453</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2909.5963</v>
-      </c>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>29.9376</v>
+        <v>0.1768</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>北京岚锋</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>10777.5453</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2909.5963</v>
       </c>
@@ -1630,1411 +1464,2043 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>2909.5963</v>
+        <v>1294.9351</v>
       </c>
       <c r="I30" t="n">
-        <v>29.9376</v>
+        <v>13.3239</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>2909.5963</v>
+        <v>913.5841</v>
       </c>
       <c r="I31" t="n">
-        <v>29.9376</v>
+        <v>9.4001</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>2909.5963</v>
+        <v>848.7142</v>
       </c>
       <c r="I32" t="n">
-        <v>29.9376</v>
+        <v>8.732699999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2909.5963</v>
+        <v>395.2401</v>
       </c>
       <c r="I33" t="n">
-        <v>29.9376</v>
+        <v>4.0667</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2909.5963</v>
+        <v>387.8661</v>
       </c>
       <c r="I34" t="n">
-        <v>29.9376</v>
+        <v>3.9909</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>2909.5963</v>
+        <v>359.628</v>
       </c>
       <c r="I35" t="n">
-        <v>29.9376</v>
+        <v>3.7003</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>2909.5963</v>
+        <v>316.1921</v>
       </c>
       <c r="I36" t="n">
-        <v>29.9376</v>
+        <v>3.2534</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2909.5963</v>
+        <v>263.6237</v>
       </c>
       <c r="I37" t="n">
-        <v>29.9376</v>
+        <v>2.7125</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2909.5963</v>
+        <v>259.2063</v>
       </c>
       <c r="I38" t="n">
-        <v>29.9376</v>
+        <v>2.667</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>2909.5963</v>
+        <v>246.0118</v>
       </c>
       <c r="I39" t="n">
-        <v>29.9376</v>
+        <v>2.5313</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>2909.5963</v>
+        <v>246.0083</v>
       </c>
       <c r="I40" t="n">
-        <v>29.9376</v>
+        <v>2.5312</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>股份公司设立时（2020年1月18日）</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>北京岚锋</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>10777.5453</v>
-      </c>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>2909.5963</v>
+        <v>172.3849</v>
       </c>
       <c r="I41" t="n">
-        <v>29.9376</v>
+        <v>1.7737</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>影石创新设立时，股本结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EARN ACE</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>4796.6179</v>
-      </c>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1294.9351</v>
+        <v>162.1267</v>
       </c>
       <c r="I42" t="n">
-        <v>13.3239</v>
+        <v>1.6682</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东EARN ACE持有4796.6179万股，持股比例13.3239%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>QM101</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>3384.0413</v>
-      </c>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>913.5841</v>
+        <v>157.9312</v>
       </c>
       <c r="I43" t="n">
-        <v>9.4001</v>
+        <v>1.625</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东QM101持有3384.0413万股，持股比例9.4001%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>香港迅雷</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>3143.7542</v>
-      </c>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>848.7142</v>
+        <v>145.9141</v>
       </c>
       <c r="I44" t="n">
-        <v>8.732699999999999</v>
+        <v>1.5013</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东香港迅雷持有3143.7542万股，持股比例8.7327%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>岚沣管理</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1464.0237</v>
-      </c>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>395.2401</v>
+        <v>126.3558</v>
       </c>
       <c r="I45" t="n">
-        <v>4.0667</v>
+        <v>1.3001</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东岚沣管理持有1464.0237万股，持股比例4.0667%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>华金同达</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1436.7094</v>
-      </c>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>387.8661</v>
+        <v>122.9215</v>
       </c>
       <c r="I46" t="n">
-        <v>3.9909</v>
+        <v>1.2648</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东华金同达持有1436.7094万股，持股比例3.9909%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>厦门富凯</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>1332.1116</v>
-      </c>
+          <t>德朴投资</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>359.628</v>
+        <v>77.49850000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>3.7003</v>
+        <v>0.7974</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东厦门富凯持有1332.1116万股，持股比例3.7003%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>澜烽管理</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>1171.2193</v>
-      </c>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>316.1921</v>
+        <v>60.7422</v>
       </c>
       <c r="I48" t="n">
-        <v>3.2534</v>
+        <v>0.625</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东澜烽管理持有1171.2193万股，持股比例3.2534%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>伊敦传媒</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>976.4985</v>
-      </c>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>263.6237</v>
+        <v>58.3132</v>
       </c>
       <c r="I49" t="n">
-        <v>2.7125</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东伊敦传媒持有976.4985万股，持股比例2.7125%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>领誉基石</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>960.1358</v>
-      </c>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>259.2063</v>
+        <v>51.7155</v>
       </c>
       <c r="I50" t="n">
-        <v>2.667</v>
+        <v>0.5321</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东领誉基石持有960.1358万股，持股比例2.667%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>中证投资</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>911.2616</v>
-      </c>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>246.0118</v>
+        <v>42.5193</v>
       </c>
       <c r="I51" t="n">
-        <v>2.5313</v>
+        <v>0.4375</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东中证投资持有911.2616万股，持股比例2.5313%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>金石智娱</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>911.2486</v>
-      </c>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>246.0083</v>
+        <v>39.37</v>
       </c>
       <c r="I52" t="n">
-        <v>2.5312</v>
+        <v>0.4051</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东金石智娱持有911.2486万股，持股比例2.5312%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>芜湖旷沄</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>638.5374</v>
-      </c>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>172.3849</v>
+        <v>24.2963</v>
       </c>
       <c r="I53" t="n">
-        <v>1.7737</v>
+        <v>0.25</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东芜湖旷沄持有638.5374万股，持股比例1.7737%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>朗玛六号</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>600.5396</v>
-      </c>
+          <t>山东龙兴(SS)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>162.1267</v>
+        <v>18.986</v>
       </c>
       <c r="I54" t="n">
-        <v>1.6682</v>
+        <v>0.1954</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东朗玛六号持有600.5396万股，持股比例1.6682%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>天正投资</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>584.9989</v>
-      </c>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>157.9312</v>
+        <v>17.1799</v>
       </c>
       <c r="I55" t="n">
-        <v>1.625</v>
+        <v>0.1768</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东天正投资持有584.9989万股，持股比例1.625%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>36000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>朗玛五号</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>540.4859</v>
-      </c>
+          <t>9,718.8612</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>145.9141</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.5013</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东朗玛五号持有540.4859万股，持股比例1.5013%（招股书第99页）</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>汇智同裕</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>478.6264</v>
-      </c>
-      <c r="H57" t="n">
-        <v>51.7155</v>
-      </c>
+          <t>北京岚锋</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>1.3295</v>
+        <v>29.9376</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东汇智同裕持有478.6264万股，持股比例1.3295%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>深圳麦高</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>468.0393</v>
-      </c>
-      <c r="H58" t="n">
-        <v>126.3558</v>
-      </c>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>1.3001</v>
+        <v>13.3239</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东深圳麦高持有468.0393万股，持股比例1.3001%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>朗玛九号</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>455.3182</v>
-      </c>
-      <c r="H59" t="n">
-        <v>122.9215</v>
-      </c>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>1.2648</v>
+        <v>9.4001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东朗玛九号持有455.3182万股，持股比例1.2648%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>朗玛十四号</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>224.9975</v>
-      </c>
-      <c r="H60" t="n">
-        <v>60.7422</v>
-      </c>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>0.625</v>
+        <v>8.732699999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东朗玛十四号持有224.9975万股，持股比例0.625%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>利得鑫投</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>216.0001</v>
-      </c>
-      <c r="H61" t="n">
-        <v>58.3132</v>
-      </c>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4.0667</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东利得鑫投持有216.0001万股，持股比例0.6%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>华金创盈</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>157.4973</v>
-      </c>
-      <c r="H62" t="n">
-        <v>42.5193</v>
-      </c>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>0.4375</v>
+        <v>3.9909</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东华金创盈持有157.4973万股，持股比例0.4375%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>岚烽管理</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>145.8319</v>
-      </c>
-      <c r="H63" t="n">
-        <v>39.37</v>
-      </c>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>0.4051</v>
+        <v>3.7003</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东岚烽管理持有145.8319万股，持股比例0.4051%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>威明投资</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>89.99679999999999</v>
-      </c>
-      <c r="H64" t="n">
-        <v>24.2963</v>
-      </c>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>0.25</v>
+        <v>3.2534</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东威明投资持有89.9968万股，持股比例0.25%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>山东龙兴（SS）</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>70.32680000000001</v>
-      </c>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>0.1954</v>
+        <v>2.7125</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>影石创新首次公开发行股票，发行前股东山东龙兴（SS）持有70.3268万股，持股比例0.1954%（招股书第99页）</t>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>发行前（第99页）</t>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>本次发行前公司股权结构</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>36000</v>
-      </c>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>2.5313</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>0</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>2.5312</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>0</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>1.7737</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>0</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>1.6682</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>0</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>0</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>0</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>1.3295</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>0</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>1.3001</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>0</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>1.2648</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>山东龙兴(SS)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>知盛投资</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>63.6367</v>
-      </c>
-      <c r="H66" t="n">
-        <v>17.1799</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
         <v>0.1768</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>0</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>刘靖康</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>0</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>刘亮</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>陈永强</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>高飞</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>贾顺</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>姜文杰</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>郭奕滨</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1、EARN ACE | 2、QM101</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1、EARN ACE | 2、QM101</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>QIMING VENTURE</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>96.94</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、EARN ACE | 2、QM101, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1、EARN ACE | 2、QM101</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1、EARN ACE | 2、QM101</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>QIMING MANAGING</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Markdown表格: 1、EARN ACE | 2、QM101, 比例合计100.0%</t>
         </is>
       </c>
     </row>
